--- a/Supplementary Information/Bentley 2025 Supplementary tables 28 feb 2025.xlsx
+++ b/Supplementary Information/Bentley 2025 Supplementary tables 28 feb 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/sl22263_bristol_ac_uk/Documents/Documents/Thesis chapters/Chapter 3 Pharyngeal jaws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="616" documentId="8_{A8710DAD-EC35-4965-A9FB-FDCCD3FAC39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A754111-29CC-4599-85D6-DF16D6BCCD84}"/>
+  <xr:revisionPtr revIDLastSave="625" documentId="8_{A8710DAD-EC35-4965-A9FB-FDCCD3FAC39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{347D57DD-3562-4956-9143-83C3F1E8D530}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C95B90AB-D662-49E3-B493-15F33E13633F}"/>
   </bookViews>
@@ -38,14 +38,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="420">
   <si>
     <t>Astroblepus</t>
   </si>
   <si>
-    <t xml:space="preserve">Genera </t>
-  </si>
-  <si>
     <t>Species</t>
   </si>
   <si>
@@ -466,9 +463,6 @@
     <t>BMNH1845.6.22.307</t>
   </si>
   <si>
-    <t>BMNH1907.7.7.6.22</t>
-  </si>
-  <si>
     <t>BMNH1972.7.17.181-183</t>
   </si>
   <si>
@@ -3619,6 +3613,15 @@
   </si>
   <si>
     <t>aureatus</t>
+  </si>
+  <si>
+    <t>Outgroup:</t>
+  </si>
+  <si>
+    <t>Cichlid comparison:</t>
+  </si>
+  <si>
+    <t>BMNH1907.7.6.22</t>
   </si>
 </sst>
 </file>
@@ -3755,28 +3758,28 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4112,2370 +4115,2453 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE41F3F-A406-4AA8-A0BA-D0058D2EAF53}">
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="4" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.36328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.08984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="229.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="229.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4">
+        <v>4.3434E-2</v>
+      </c>
+      <c r="E4">
+        <v>120</v>
+      </c>
+      <c r="F4">
+        <v>225</v>
+      </c>
+      <c r="H4">
+        <v>708</v>
+      </c>
+      <c r="I4">
+        <v>2750</v>
+      </c>
+      <c r="J4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5">
+        <v>4.4517000000000001E-2</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>310</v>
+      </c>
+      <c r="G5">
+        <v>31</v>
+      </c>
+      <c r="H5">
+        <v>250</v>
+      </c>
+      <c r="I5">
+        <v>3786</v>
+      </c>
+      <c r="J5" t="s">
+        <v>191</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5" t="s">
+        <v>194</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D6">
+        <v>4.2831000000000001E-2</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>310</v>
+      </c>
+      <c r="G6">
+        <v>31</v>
+      </c>
+      <c r="H6">
+        <v>250</v>
+      </c>
+      <c r="I6">
+        <v>4200</v>
+      </c>
+      <c r="J6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6" t="s">
+        <v>194</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7">
+        <v>3.3521000000000002E-2</v>
+      </c>
+      <c r="E7">
+        <v>120</v>
+      </c>
+      <c r="F7">
+        <v>144</v>
+      </c>
+      <c r="H7">
+        <v>708</v>
+      </c>
+      <c r="I7">
+        <v>2750</v>
+      </c>
+      <c r="J7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8">
+        <v>1.9765000000000001E-2</v>
+      </c>
+      <c r="E8">
+        <v>120</v>
+      </c>
+      <c r="F8">
+        <v>140</v>
+      </c>
+      <c r="H8">
+        <v>708</v>
+      </c>
+      <c r="I8">
+        <v>2750</v>
+      </c>
+      <c r="J8" t="s">
+        <v>190</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9">
+        <v>2.8528000000000001E-2</v>
+      </c>
+      <c r="E9">
+        <v>120</v>
+      </c>
+      <c r="F9">
+        <v>225</v>
+      </c>
+      <c r="H9">
+        <v>708</v>
+      </c>
+      <c r="I9">
+        <v>2750</v>
+      </c>
+      <c r="J9" t="s">
+        <v>190</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10">
+        <v>2.8528000000000001E-2</v>
+      </c>
+      <c r="E10">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>225</v>
+      </c>
+      <c r="H10">
+        <v>708</v>
+      </c>
+      <c r="I10">
+        <v>2750</v>
+      </c>
+      <c r="J10" t="s">
+        <v>190</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11">
+        <v>1.6060999999999999E-2</v>
+      </c>
+      <c r="E11">
+        <v>120</v>
+      </c>
+      <c r="F11">
+        <v>140</v>
+      </c>
+      <c r="H11">
+        <v>708</v>
+      </c>
+      <c r="I11">
+        <v>2750</v>
+      </c>
+      <c r="J11" t="s">
+        <v>190</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12">
+        <v>1.5386E-2</v>
+      </c>
+      <c r="E12">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>144</v>
+      </c>
+      <c r="H12">
+        <v>708</v>
+      </c>
+      <c r="I12">
+        <v>2750</v>
+      </c>
+      <c r="J12" t="s">
+        <v>190</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13">
+        <v>4.6716000000000001E-2</v>
+      </c>
+      <c r="E13">
+        <v>120</v>
+      </c>
+      <c r="F13">
+        <v>225</v>
+      </c>
+      <c r="H13">
+        <v>708</v>
+      </c>
+      <c r="I13">
+        <v>2750</v>
+      </c>
+      <c r="J13" t="s">
+        <v>190</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14">
+        <v>7.0460000000000002E-3</v>
+      </c>
+      <c r="E14">
+        <v>120</v>
+      </c>
+      <c r="F14">
+        <v>144</v>
+      </c>
+      <c r="H14">
+        <v>708</v>
+      </c>
+      <c r="I14">
+        <v>2750</v>
+      </c>
+      <c r="J14" t="s">
+        <v>190</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15">
+        <v>2.8528000000000001E-2</v>
+      </c>
+      <c r="E15">
+        <v>120</v>
+      </c>
+      <c r="F15">
+        <v>225</v>
+      </c>
+      <c r="H15">
+        <v>708</v>
+      </c>
+      <c r="I15">
+        <v>2750</v>
+      </c>
+      <c r="J15" t="s">
+        <v>190</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16">
+        <v>7.4739999999999997E-3</v>
+      </c>
+      <c r="E16">
+        <v>120</v>
+      </c>
+      <c r="F16">
+        <v>62</v>
+      </c>
+      <c r="H16">
+        <v>708</v>
+      </c>
+      <c r="I16">
+        <v>2750</v>
+      </c>
+      <c r="J16" t="s">
+        <v>190</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17">
+        <v>2.9884999999999998E-2</v>
+      </c>
+      <c r="E17">
+        <v>120</v>
+      </c>
+      <c r="F17">
+        <v>225</v>
+      </c>
+      <c r="H17">
+        <v>708</v>
+      </c>
+      <c r="I17">
+        <v>2750</v>
+      </c>
+      <c r="J17" t="s">
+        <v>190</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18">
+        <v>2.4967E-2</v>
+      </c>
+      <c r="E18">
+        <v>120</v>
+      </c>
+      <c r="F18">
+        <v>208</v>
+      </c>
+      <c r="H18">
+        <v>708</v>
+      </c>
+      <c r="I18">
+        <v>2750</v>
+      </c>
+      <c r="J18" t="s">
+        <v>190</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19">
+        <v>7.3990000000000002E-3</v>
+      </c>
+      <c r="E19">
+        <v>120</v>
+      </c>
+      <c r="F19">
+        <v>144</v>
+      </c>
+      <c r="H19">
+        <v>708</v>
+      </c>
+      <c r="I19">
+        <v>2750</v>
+      </c>
+      <c r="J19" t="s">
+        <v>190</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20">
+        <v>2.5055999999999998E-2</v>
+      </c>
+      <c r="E20">
+        <v>95</v>
+      </c>
+      <c r="F20">
+        <v>253</v>
+      </c>
+      <c r="H20">
+        <v>708</v>
+      </c>
+      <c r="I20">
+        <v>2750</v>
+      </c>
+      <c r="J20" t="s">
+        <v>190</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21">
+        <v>2.4514000000000001E-2</v>
+      </c>
+      <c r="E21">
+        <v>120</v>
+      </c>
+      <c r="F21">
+        <v>204</v>
+      </c>
+      <c r="H21">
+        <v>708</v>
+      </c>
+      <c r="I21">
+        <v>2750</v>
+      </c>
+      <c r="J21" t="s">
+        <v>190</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22">
+        <v>1.5633999999999999E-2</v>
+      </c>
+      <c r="E22">
+        <v>120</v>
+      </c>
+      <c r="F22">
+        <v>144</v>
+      </c>
+      <c r="H22">
+        <v>708</v>
+      </c>
+      <c r="I22">
+        <v>2750</v>
+      </c>
+      <c r="J22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" s="13">
+        <v>2.7602439999999999E-2</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="L23" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24">
+        <v>2.4514000000000001E-2</v>
+      </c>
+      <c r="E24">
+        <v>120</v>
+      </c>
+      <c r="F24">
+        <v>204</v>
+      </c>
+      <c r="H24">
+        <v>708</v>
+      </c>
+      <c r="I24">
+        <v>2750</v>
+      </c>
+      <c r="J24" t="s">
+        <v>190</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25">
+        <v>1.9803999999999999E-2</v>
+      </c>
+      <c r="E25">
+        <v>120</v>
+      </c>
+      <c r="F25">
+        <v>140</v>
+      </c>
+      <c r="H25">
+        <v>708</v>
+      </c>
+      <c r="I25">
+        <v>2750</v>
+      </c>
+      <c r="J25" t="s">
+        <v>190</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26">
+        <v>2.8885000000000001E-2</v>
+      </c>
+      <c r="E26">
+        <v>120</v>
+      </c>
+      <c r="F26">
+        <v>140</v>
+      </c>
+      <c r="H26">
+        <v>708</v>
+      </c>
+      <c r="I26">
+        <v>2750</v>
+      </c>
+      <c r="J26" t="s">
+        <v>190</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27">
+        <v>5.8525000000000001E-2</v>
+      </c>
+      <c r="E27">
+        <v>120</v>
+      </c>
+      <c r="F27">
+        <v>140</v>
+      </c>
+      <c r="H27">
+        <v>708</v>
+      </c>
+      <c r="I27">
+        <v>2750</v>
+      </c>
+      <c r="J27" t="s">
+        <v>190</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28">
+        <v>1.6060999999999999E-2</v>
+      </c>
+      <c r="E28">
+        <v>120</v>
+      </c>
+      <c r="F28">
+        <v>140</v>
+      </c>
+      <c r="H28">
+        <v>708</v>
+      </c>
+      <c r="I28">
+        <v>2750</v>
+      </c>
+      <c r="J28" t="s">
+        <v>190</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>419</v>
+      </c>
+      <c r="D29">
+        <v>2.6789E-2</v>
+      </c>
+      <c r="E29">
+        <v>120</v>
+      </c>
+      <c r="F29">
+        <v>140</v>
+      </c>
+      <c r="H29">
+        <v>708</v>
+      </c>
+      <c r="I29">
+        <v>2750</v>
+      </c>
+      <c r="J29" t="s">
+        <v>190</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D30">
+        <v>4.4047999999999997E-2</v>
+      </c>
+      <c r="E30">
+        <v>120</v>
+      </c>
+      <c r="F30">
+        <v>225</v>
+      </c>
+      <c r="H30">
+        <v>708</v>
+      </c>
+      <c r="I30">
+        <v>2750</v>
+      </c>
+      <c r="J30" t="s">
+        <v>190</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31">
+        <v>2.7623999999999999E-2</v>
+      </c>
+      <c r="E31">
+        <v>120</v>
+      </c>
+      <c r="F31">
+        <v>161</v>
+      </c>
+      <c r="H31">
+        <v>708</v>
+      </c>
+      <c r="I31">
+        <v>2750</v>
+      </c>
+      <c r="J31" t="s">
+        <v>190</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32">
+        <v>1.5009E-2</v>
+      </c>
+      <c r="E32">
+        <v>120</v>
+      </c>
+      <c r="F32">
+        <v>144</v>
+      </c>
+      <c r="H32">
+        <v>708</v>
+      </c>
+      <c r="I32">
+        <v>2750</v>
+      </c>
+      <c r="J32" t="s">
+        <v>190</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33">
+        <v>5.3245000000000001E-2</v>
+      </c>
+      <c r="E33">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>310</v>
+      </c>
+      <c r="G33">
+        <v>31</v>
+      </c>
+      <c r="H33">
+        <v>250</v>
+      </c>
+      <c r="I33">
+        <v>3025</v>
+      </c>
+      <c r="J33" t="s">
+        <v>191</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33" t="s">
+        <v>194</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34">
+        <v>1.5633999999999999E-2</v>
+      </c>
+      <c r="E34">
+        <v>120</v>
+      </c>
+      <c r="F34">
+        <v>144</v>
+      </c>
+      <c r="H34">
+        <v>708</v>
+      </c>
+      <c r="I34">
+        <v>2750</v>
+      </c>
+      <c r="J34" t="s">
+        <v>190</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35">
+        <v>1.2848999999999999E-2</v>
+      </c>
+      <c r="E35">
+        <v>120</v>
+      </c>
+      <c r="F35">
+        <v>144</v>
+      </c>
+      <c r="H35">
+        <v>708</v>
+      </c>
+      <c r="I35">
+        <v>2750</v>
+      </c>
+      <c r="J35" t="s">
+        <v>190</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36">
+        <v>3.4110021999999997E-2</v>
+      </c>
+      <c r="L36" t="s">
+        <v>200</v>
+      </c>
+      <c r="M36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37">
+        <v>7.0179999999999999E-3</v>
+      </c>
+      <c r="E37">
+        <v>120</v>
+      </c>
+      <c r="F37">
+        <v>144</v>
+      </c>
+      <c r="H37">
+        <v>708</v>
+      </c>
+      <c r="I37">
+        <v>2750</v>
+      </c>
+      <c r="J37" t="s">
+        <v>190</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38">
+        <v>1.2848999999999999E-2</v>
+      </c>
+      <c r="E38">
+        <v>120</v>
+      </c>
+      <c r="F38">
+        <v>144</v>
+      </c>
+      <c r="H38">
+        <v>708</v>
+      </c>
+      <c r="I38">
+        <v>2750</v>
+      </c>
+      <c r="J38" t="s">
+        <v>190</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39">
+        <v>2.2934E-2</v>
+      </c>
+      <c r="E39">
+        <v>120</v>
+      </c>
+      <c r="F39">
+        <v>140</v>
+      </c>
+      <c r="H39">
+        <v>708</v>
+      </c>
+      <c r="I39">
+        <v>2750</v>
+      </c>
+      <c r="J39" t="s">
+        <v>190</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40">
+        <v>7.0179999999999999E-3</v>
+      </c>
+      <c r="E40">
+        <v>120</v>
+      </c>
+      <c r="F40">
+        <v>144</v>
+      </c>
+      <c r="H40">
+        <v>708</v>
+      </c>
+      <c r="I40">
+        <v>2750</v>
+      </c>
+      <c r="J40" t="s">
+        <v>190</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41">
+        <v>4.9220000000000002E-3</v>
+      </c>
+      <c r="E41">
+        <v>120</v>
+      </c>
+      <c r="F41">
+        <v>144</v>
+      </c>
+      <c r="H41">
+        <v>708</v>
+      </c>
+      <c r="I41">
+        <v>2750</v>
+      </c>
+      <c r="J41" t="s">
+        <v>190</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D42">
+        <v>2.4514000000000001E-2</v>
+      </c>
+      <c r="E42">
+        <v>120</v>
+      </c>
+      <c r="F42">
+        <v>204</v>
+      </c>
+      <c r="H42">
+        <v>708</v>
+      </c>
+      <c r="I42">
+        <v>2750</v>
+      </c>
+      <c r="J42" t="s">
+        <v>190</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43">
+        <v>2.4514000000000001E-2</v>
+      </c>
+      <c r="E43">
+        <v>120</v>
+      </c>
+      <c r="F43">
+        <v>204</v>
+      </c>
+      <c r="H43">
+        <v>708</v>
+      </c>
+      <c r="I43">
+        <v>2750</v>
+      </c>
+      <c r="J43" t="s">
+        <v>190</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44">
+        <v>2.4531000000000001E-2</v>
+      </c>
+      <c r="E44">
+        <v>95</v>
+      </c>
+      <c r="F44">
+        <v>253</v>
+      </c>
+      <c r="H44">
+        <v>708</v>
+      </c>
+      <c r="I44">
+        <v>2750</v>
+      </c>
+      <c r="J44" t="s">
+        <v>190</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45">
+        <v>2.5055999999999998E-2</v>
+      </c>
+      <c r="E45">
+        <v>95</v>
+      </c>
+      <c r="F45">
+        <v>253</v>
+      </c>
+      <c r="H45">
+        <v>708</v>
+      </c>
+      <c r="I45">
+        <v>2750</v>
+      </c>
+      <c r="J45" t="s">
+        <v>190</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46">
+        <v>1.9403E-2</v>
+      </c>
+      <c r="E46">
+        <v>115</v>
+      </c>
+      <c r="F46">
+        <v>235</v>
+      </c>
+      <c r="H46">
+        <v>708</v>
+      </c>
+      <c r="I46">
+        <v>2750</v>
+      </c>
+      <c r="J46" t="s">
+        <v>190</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" t="s">
+        <v>158</v>
+      </c>
+      <c r="D47">
+        <v>1.7330000000000002E-2</v>
+      </c>
+      <c r="E47">
+        <v>120</v>
+      </c>
+      <c r="F47">
+        <v>144</v>
+      </c>
+      <c r="H47">
+        <v>708</v>
+      </c>
+      <c r="I47">
+        <v>2750</v>
+      </c>
+      <c r="J47" t="s">
+        <v>190</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48">
+        <v>2.1069999999999998E-2</v>
+      </c>
+      <c r="E48">
+        <v>120</v>
+      </c>
+      <c r="F48">
+        <v>144</v>
+      </c>
+      <c r="H48">
+        <v>708</v>
+      </c>
+      <c r="I48">
+        <v>2750</v>
+      </c>
+      <c r="J48" t="s">
+        <v>190</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49">
+        <v>5.3449999999999999E-3</v>
+      </c>
+      <c r="E49">
+        <v>120</v>
+      </c>
+      <c r="F49">
+        <v>144</v>
+      </c>
+      <c r="H49">
+        <v>708</v>
+      </c>
+      <c r="I49">
+        <v>2750</v>
+      </c>
+      <c r="J49" t="s">
+        <v>190</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" t="s">
+        <v>161</v>
+      </c>
+      <c r="D50">
+        <v>1.7330000000000002E-2</v>
+      </c>
+      <c r="E50">
+        <v>120</v>
+      </c>
+      <c r="F50">
+        <v>225</v>
+      </c>
+      <c r="H50">
+        <v>708</v>
+      </c>
+      <c r="I50">
+        <v>2750</v>
+      </c>
+      <c r="J50" t="s">
+        <v>190</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" t="s">
+        <v>162</v>
+      </c>
+      <c r="D51">
+        <v>2.8885000000000001E-2</v>
+      </c>
+      <c r="E51">
+        <v>120</v>
+      </c>
+      <c r="F51">
+        <v>140</v>
+      </c>
+      <c r="H51">
+        <v>708</v>
+      </c>
+      <c r="I51">
+        <v>2750</v>
+      </c>
+      <c r="J51" t="s">
+        <v>190</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" t="s">
+        <v>163</v>
+      </c>
+      <c r="D52">
+        <v>1.5386E-2</v>
+      </c>
+      <c r="E52">
+        <v>120</v>
+      </c>
+      <c r="F52">
+        <v>144</v>
+      </c>
+      <c r="H52">
+        <v>708</v>
+      </c>
+      <c r="I52">
+        <v>2750</v>
+      </c>
+      <c r="J52" t="s">
+        <v>190</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53">
+        <v>3.9204000000000003E-2</v>
+      </c>
+      <c r="E53">
+        <v>120</v>
+      </c>
+      <c r="H53">
+        <v>708</v>
+      </c>
+      <c r="I53">
+        <v>2750</v>
+      </c>
+      <c r="J53" t="s">
+        <v>190</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D54">
+        <v>5.1914000000000002E-2</v>
+      </c>
+      <c r="E54">
+        <v>85</v>
+      </c>
+      <c r="F54">
+        <v>297</v>
+      </c>
+      <c r="H54">
+        <v>708</v>
+      </c>
+      <c r="I54">
+        <v>2750</v>
+      </c>
+      <c r="J54" t="s">
+        <v>190</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D55">
+        <v>3.3673279061519699E-2</v>
+      </c>
+      <c r="E55">
+        <v>120</v>
+      </c>
+      <c r="F55">
+        <v>225</v>
+      </c>
+      <c r="H55">
+        <v>708</v>
+      </c>
+      <c r="I55">
+        <v>2750</v>
+      </c>
+      <c r="J55" t="s">
+        <v>190</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56">
+        <v>4.25034931994452E-2</v>
+      </c>
+      <c r="E56">
+        <v>120</v>
+      </c>
+      <c r="F56">
+        <v>225</v>
+      </c>
+      <c r="H56">
+        <v>708</v>
+      </c>
+      <c r="I56">
+        <v>2750</v>
+      </c>
+      <c r="J56" t="s">
+        <v>190</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57">
+        <v>3.3515999999999997E-2</v>
+      </c>
+      <c r="E57">
+        <v>120</v>
+      </c>
+      <c r="F57">
+        <v>225</v>
+      </c>
+      <c r="H57">
+        <v>708</v>
+      </c>
+      <c r="I57">
+        <v>2750</v>
+      </c>
+      <c r="J57" t="s">
+        <v>190</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" t="s">
+        <v>169</v>
+      </c>
+      <c r="D58">
+        <v>2.9884999999999998E-2</v>
+      </c>
+      <c r="E58">
+        <v>120</v>
+      </c>
+      <c r="F58">
+        <v>225</v>
+      </c>
+      <c r="H58">
+        <v>708</v>
+      </c>
+      <c r="I58">
+        <v>2750</v>
+      </c>
+      <c r="J58" t="s">
+        <v>190</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D59">
+        <v>2.6974999999999999E-2</v>
+      </c>
+      <c r="E59">
+        <v>120</v>
+      </c>
+      <c r="F59">
+        <v>161</v>
+      </c>
+      <c r="H59">
+        <v>708</v>
+      </c>
+      <c r="I59">
+        <v>2750</v>
+      </c>
+      <c r="J59" t="s">
+        <v>190</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" t="s">
+        <v>171</v>
+      </c>
+      <c r="D60">
+        <v>4.9220000000000002E-3</v>
+      </c>
+      <c r="E60">
+        <v>120</v>
+      </c>
+      <c r="F60">
+        <v>144</v>
+      </c>
+      <c r="H60">
+        <v>708</v>
+      </c>
+      <c r="I60">
+        <v>2750</v>
+      </c>
+      <c r="J60" t="s">
+        <v>190</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" t="s">
+        <v>119</v>
+      </c>
+      <c r="D61">
+        <v>4.4047999999999997E-2</v>
+      </c>
+      <c r="E61">
+        <v>120</v>
+      </c>
+      <c r="F61">
+        <v>225</v>
+      </c>
+      <c r="H61">
+        <v>708</v>
+      </c>
+      <c r="I61">
+        <v>2750</v>
+      </c>
+      <c r="J61" t="s">
+        <v>190</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62">
+        <v>2.5055999999999998E-2</v>
+      </c>
+      <c r="E62">
+        <v>95</v>
+      </c>
+      <c r="F62">
+        <v>253</v>
+      </c>
+      <c r="H62">
+        <v>708</v>
+      </c>
+      <c r="I62">
+        <v>2750</v>
+      </c>
+      <c r="J62" t="s">
+        <v>190</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C63" t="s">
+        <v>174</v>
+      </c>
+      <c r="D63">
+        <v>5.1914000000000002E-2</v>
+      </c>
+      <c r="E63">
+        <v>85</v>
+      </c>
+      <c r="F63">
+        <v>297</v>
+      </c>
+      <c r="H63">
+        <v>708</v>
+      </c>
+      <c r="I63">
+        <v>2750</v>
+      </c>
+      <c r="J63" t="s">
+        <v>190</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64">
+        <v>4.25034931994452E-2</v>
+      </c>
+      <c r="E64">
+        <v>120</v>
+      </c>
+      <c r="F64">
+        <v>225</v>
+      </c>
+      <c r="H64">
+        <v>708</v>
+      </c>
+      <c r="I64">
+        <v>2750</v>
+      </c>
+      <c r="J64" t="s">
+        <v>190</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" t="s">
+        <v>119</v>
+      </c>
+      <c r="D65">
+        <v>2.8528000000000001E-2</v>
+      </c>
+      <c r="E65">
+        <v>120</v>
+      </c>
+      <c r="F65">
+        <v>225</v>
+      </c>
+      <c r="H65">
+        <v>708</v>
+      </c>
+      <c r="I65">
+        <v>2750</v>
+      </c>
+      <c r="J65" t="s">
+        <v>190</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66">
+        <v>2.8528000000000001E-2</v>
+      </c>
+      <c r="E66">
+        <v>120</v>
+      </c>
+      <c r="F66">
+        <v>225</v>
+      </c>
+      <c r="H66">
+        <v>708</v>
+      </c>
+      <c r="I66">
+        <v>2750</v>
+      </c>
+      <c r="J66" t="s">
+        <v>190</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D67">
+        <v>2.2934E-2</v>
+      </c>
+      <c r="E67">
+        <v>120</v>
+      </c>
+      <c r="F67">
+        <v>140</v>
+      </c>
+      <c r="H67">
+        <v>708</v>
+      </c>
+      <c r="I67">
+        <v>2750</v>
+      </c>
+      <c r="J67" t="s">
+        <v>190</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" t="s">
+        <v>176</v>
+      </c>
+      <c r="D68">
+        <v>3.9204000000000003E-2</v>
+      </c>
+      <c r="E68">
+        <v>120</v>
+      </c>
+      <c r="F68">
+        <v>225</v>
+      </c>
+      <c r="H68">
+        <v>708</v>
+      </c>
+      <c r="I68">
+        <v>2750</v>
+      </c>
+      <c r="J68" t="s">
+        <v>190</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="C69" t="s">
+        <v>180</v>
+      </c>
+      <c r="D69" s="17">
+        <v>4.7503619965347202E-2</v>
+      </c>
+      <c r="E69">
+        <v>90</v>
+      </c>
+      <c r="F69">
+        <v>416</v>
+      </c>
+      <c r="G69">
+        <v>37.44</v>
+      </c>
+      <c r="H69">
+        <v>354</v>
+      </c>
+      <c r="I69">
+        <v>1001</v>
+      </c>
+      <c r="J69" t="s">
+        <v>191</v>
+      </c>
+      <c r="L69" t="s">
+        <v>196</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71">
+        <v>1.9765000000000001E-2</v>
+      </c>
+      <c r="E71">
+        <v>120</v>
+      </c>
+      <c r="F71">
+        <v>140</v>
+      </c>
+      <c r="H71">
+        <v>708</v>
+      </c>
+      <c r="I71">
+        <v>2750</v>
+      </c>
+      <c r="J71" t="s">
         <v>190</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A73" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D73" s="15">
+        <v>4.7503619965347202E-2</v>
+      </c>
+      <c r="E73" s="1">
+        <v>90</v>
+      </c>
+      <c r="F73" s="1">
+        <v>416</v>
+      </c>
+      <c r="G73" s="1">
+        <v>37.44</v>
+      </c>
+      <c r="H73" s="1">
+        <v>354</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1001</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="3">
-        <v>4.3434E-2</v>
-      </c>
-      <c r="E4" s="3">
-        <v>120</v>
-      </c>
-      <c r="F4" s="3">
-        <v>225</v>
-      </c>
-      <c r="H4" s="3">
-        <v>708</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4.4517000000000001E-2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>100</v>
-      </c>
-      <c r="F5" s="3">
-        <v>310</v>
-      </c>
-      <c r="G5" s="3">
-        <v>31</v>
-      </c>
-      <c r="H5" s="3">
-        <v>250</v>
-      </c>
-      <c r="I5" s="3">
-        <v>3786</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K5" s="3">
-        <v>2</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="K73" s="1"/>
+      <c r="L73" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M5" s="10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" s="3">
-        <v>4.2831000000000001E-2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>100</v>
-      </c>
-      <c r="F6" s="3">
-        <v>310</v>
-      </c>
-      <c r="G6" s="3">
-        <v>31</v>
-      </c>
-      <c r="H6" s="3">
-        <v>250</v>
-      </c>
-      <c r="I6" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K6" s="3">
-        <v>2</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3.3521000000000002E-2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>120</v>
-      </c>
-      <c r="F7" s="3">
-        <v>144</v>
-      </c>
-      <c r="H7" s="3">
-        <v>708</v>
-      </c>
-      <c r="I7" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1.9765000000000001E-2</v>
-      </c>
-      <c r="E8" s="3">
-        <v>120</v>
-      </c>
-      <c r="F8" s="3">
-        <v>140</v>
-      </c>
-      <c r="H8" s="3">
-        <v>708</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2.8528000000000001E-2</v>
-      </c>
-      <c r="E9" s="3">
-        <v>120</v>
-      </c>
-      <c r="F9" s="3">
-        <v>225</v>
-      </c>
-      <c r="H9" s="3">
-        <v>708</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2.8528000000000001E-2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>120</v>
-      </c>
-      <c r="F10" s="3">
-        <v>225</v>
-      </c>
-      <c r="H10" s="3">
-        <v>708</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1.6060999999999999E-2</v>
-      </c>
-      <c r="E11" s="3">
-        <v>120</v>
-      </c>
-      <c r="F11" s="3">
-        <v>140</v>
-      </c>
-      <c r="H11" s="3">
-        <v>708</v>
-      </c>
-      <c r="I11" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1.5386E-2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>120</v>
-      </c>
-      <c r="F12" s="3">
-        <v>144</v>
-      </c>
-      <c r="H12" s="3">
-        <v>708</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="3">
-        <v>4.6716000000000001E-2</v>
-      </c>
-      <c r="E13" s="3">
-        <v>120</v>
-      </c>
-      <c r="F13" s="3">
-        <v>225</v>
-      </c>
-      <c r="H13" s="3">
-        <v>708</v>
-      </c>
-      <c r="I13" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K13" s="3">
-        <v>1</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="3">
-        <v>7.0460000000000002E-3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>120</v>
-      </c>
-      <c r="F14" s="3">
-        <v>144</v>
-      </c>
-      <c r="H14" s="3">
-        <v>708</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="3">
-        <v>2.8528000000000001E-2</v>
-      </c>
-      <c r="E15" s="3">
-        <v>120</v>
-      </c>
-      <c r="F15" s="3">
-        <v>225</v>
-      </c>
-      <c r="H15" s="3">
-        <v>708</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" s="3">
-        <v>7.4739999999999997E-3</v>
-      </c>
-      <c r="E16" s="3">
-        <v>120</v>
-      </c>
-      <c r="F16" s="3">
-        <v>62</v>
-      </c>
-      <c r="H16" s="3">
-        <v>708</v>
-      </c>
-      <c r="I16" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K16" s="3">
-        <v>1</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2.9884999999999998E-2</v>
-      </c>
-      <c r="E17" s="3">
-        <v>120</v>
-      </c>
-      <c r="F17" s="3">
-        <v>225</v>
-      </c>
-      <c r="H17" s="3">
-        <v>708</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" s="3">
-        <v>2.4967E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>120</v>
-      </c>
-      <c r="F18" s="3">
-        <v>208</v>
-      </c>
-      <c r="H18" s="3">
-        <v>708</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D19" s="3">
-        <v>7.3990000000000002E-3</v>
-      </c>
-      <c r="E19" s="3">
-        <v>120</v>
-      </c>
-      <c r="F19" s="3">
-        <v>144</v>
-      </c>
-      <c r="H19" s="3">
-        <v>708</v>
-      </c>
-      <c r="I19" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K19" s="3">
-        <v>1</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D20" s="3">
-        <v>2.5055999999999998E-2</v>
-      </c>
-      <c r="E20" s="3">
-        <v>95</v>
-      </c>
-      <c r="F20" s="3">
-        <v>253</v>
-      </c>
-      <c r="H20" s="3">
-        <v>708</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="3">
-        <v>2.4514000000000001E-2</v>
-      </c>
-      <c r="E21" s="3">
-        <v>120</v>
-      </c>
-      <c r="F21" s="3">
-        <v>204</v>
-      </c>
-      <c r="H21" s="3">
-        <v>708</v>
-      </c>
-      <c r="I21" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1.5633999999999999E-2</v>
-      </c>
-      <c r="E22" s="3">
-        <v>120</v>
-      </c>
-      <c r="F22" s="3">
-        <v>144</v>
-      </c>
-      <c r="H22" s="3">
-        <v>708</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2.7602439999999999E-2</v>
-      </c>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="L23" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="M23" s="14" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="3">
-        <v>2.4514000000000001E-2</v>
-      </c>
-      <c r="E24" s="3">
-        <v>120</v>
-      </c>
-      <c r="F24" s="3">
-        <v>204</v>
-      </c>
-      <c r="H24" s="3">
-        <v>708</v>
-      </c>
-      <c r="I24" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D25" s="3">
-        <v>1.9803999999999999E-2</v>
-      </c>
-      <c r="E25" s="3">
-        <v>120</v>
-      </c>
-      <c r="F25" s="3">
-        <v>140</v>
-      </c>
-      <c r="H25" s="3">
-        <v>708</v>
-      </c>
-      <c r="I25" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K25" s="3">
-        <v>1</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D26" s="3">
-        <v>2.8885000000000001E-2</v>
-      </c>
-      <c r="E26" s="3">
-        <v>120</v>
-      </c>
-      <c r="F26" s="3">
-        <v>140</v>
-      </c>
-      <c r="H26" s="3">
-        <v>708</v>
-      </c>
-      <c r="I26" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D27" s="3">
-        <v>5.8525000000000001E-2</v>
-      </c>
-      <c r="E27" s="3">
-        <v>120</v>
-      </c>
-      <c r="F27" s="3">
-        <v>140</v>
-      </c>
-      <c r="H27" s="3">
-        <v>708</v>
-      </c>
-      <c r="I27" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1.6060999999999999E-2</v>
-      </c>
-      <c r="E28" s="3">
-        <v>120</v>
-      </c>
-      <c r="F28" s="3">
-        <v>140</v>
-      </c>
-      <c r="H28" s="3">
-        <v>708</v>
-      </c>
-      <c r="I28" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K28" s="3">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="3">
-        <v>2.6789E-2</v>
-      </c>
-      <c r="E29" s="3">
-        <v>120</v>
-      </c>
-      <c r="F29" s="3">
-        <v>140</v>
-      </c>
-      <c r="H29" s="3">
-        <v>708</v>
-      </c>
-      <c r="I29" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K29" s="3">
-        <v>1</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" s="3">
-        <v>4.4047999999999997E-2</v>
-      </c>
-      <c r="E30" s="3">
-        <v>120</v>
-      </c>
-      <c r="F30" s="3">
-        <v>225</v>
-      </c>
-      <c r="H30" s="3">
-        <v>708</v>
-      </c>
-      <c r="I30" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K30" s="3">
-        <v>1</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2.7623999999999999E-2</v>
-      </c>
-      <c r="E31" s="3">
-        <v>120</v>
-      </c>
-      <c r="F31" s="3">
-        <v>161</v>
-      </c>
-      <c r="H31" s="3">
-        <v>708</v>
-      </c>
-      <c r="I31" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K31" s="3">
-        <v>1</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D32" s="3">
-        <v>1.5009E-2</v>
-      </c>
-      <c r="E32" s="3">
-        <v>120</v>
-      </c>
-      <c r="F32" s="3">
-        <v>144</v>
-      </c>
-      <c r="H32" s="3">
-        <v>708</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K32" s="3">
-        <v>1</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D33" s="3">
-        <v>5.3245000000000001E-2</v>
-      </c>
-      <c r="E33" s="3">
-        <v>100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>310</v>
-      </c>
-      <c r="G33" s="3">
-        <v>31</v>
-      </c>
-      <c r="H33" s="3">
-        <v>250</v>
-      </c>
-      <c r="I33" s="3">
-        <v>3025</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K33" s="3">
-        <v>2</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" s="3">
-        <v>1.5633999999999999E-2</v>
-      </c>
-      <c r="E34" s="3">
-        <v>120</v>
-      </c>
-      <c r="F34" s="3">
-        <v>144</v>
-      </c>
-      <c r="H34" s="3">
-        <v>708</v>
-      </c>
-      <c r="I34" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K34" s="3">
-        <v>1</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D35" s="3">
-        <v>1.2848999999999999E-2</v>
-      </c>
-      <c r="E35" s="3">
-        <v>120</v>
-      </c>
-      <c r="F35" s="3">
-        <v>144</v>
-      </c>
-      <c r="H35" s="3">
-        <v>708</v>
-      </c>
-      <c r="I35" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D36" s="3">
-        <v>3.4110021999999997E-2</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="M36" s="3" t="s">
+      <c r="M73" s="16" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" s="3">
-        <v>7.0179999999999999E-3</v>
-      </c>
-      <c r="E37" s="3">
-        <v>120</v>
-      </c>
-      <c r="F37" s="3">
-        <v>144</v>
-      </c>
-      <c r="H37" s="3">
-        <v>708</v>
-      </c>
-      <c r="I37" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K37" s="3">
-        <v>1</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1.2848999999999999E-2</v>
-      </c>
-      <c r="E38" s="3">
-        <v>120</v>
-      </c>
-      <c r="F38" s="3">
-        <v>144</v>
-      </c>
-      <c r="H38" s="3">
-        <v>708</v>
-      </c>
-      <c r="I38" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K38" s="3">
-        <v>1</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D39" s="3">
-        <v>2.2934E-2</v>
-      </c>
-      <c r="E39" s="3">
-        <v>120</v>
-      </c>
-      <c r="F39" s="3">
-        <v>140</v>
-      </c>
-      <c r="H39" s="3">
-        <v>708</v>
-      </c>
-      <c r="I39" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K39" s="3">
-        <v>1</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D40" s="3">
-        <v>7.0179999999999999E-3</v>
-      </c>
-      <c r="E40" s="3">
-        <v>120</v>
-      </c>
-      <c r="F40" s="3">
-        <v>144</v>
-      </c>
-      <c r="H40" s="3">
-        <v>708</v>
-      </c>
-      <c r="I40" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K40" s="3">
-        <v>1</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" s="3">
-        <v>4.9220000000000002E-3</v>
-      </c>
-      <c r="E41" s="3">
-        <v>120</v>
-      </c>
-      <c r="F41" s="3">
-        <v>144</v>
-      </c>
-      <c r="H41" s="3">
-        <v>708</v>
-      </c>
-      <c r="I41" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K41" s="3">
-        <v>1</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D42" s="3">
-        <v>2.4514000000000001E-2</v>
-      </c>
-      <c r="E42" s="3">
-        <v>120</v>
-      </c>
-      <c r="F42" s="3">
-        <v>204</v>
-      </c>
-      <c r="H42" s="3">
-        <v>708</v>
-      </c>
-      <c r="I42" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K42" s="3">
-        <v>1</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D43" s="3">
-        <v>2.4514000000000001E-2</v>
-      </c>
-      <c r="E43" s="3">
-        <v>120</v>
-      </c>
-      <c r="F43" s="3">
-        <v>204</v>
-      </c>
-      <c r="H43" s="3">
-        <v>708</v>
-      </c>
-      <c r="I43" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D44" s="3">
-        <v>2.4531000000000001E-2</v>
-      </c>
-      <c r="E44" s="3">
-        <v>95</v>
-      </c>
-      <c r="F44" s="3">
-        <v>253</v>
-      </c>
-      <c r="H44" s="3">
-        <v>708</v>
-      </c>
-      <c r="I44" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K44" s="3">
-        <v>1</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D45" s="3">
-        <v>2.5055999999999998E-2</v>
-      </c>
-      <c r="E45" s="3">
-        <v>95</v>
-      </c>
-      <c r="F45" s="3">
-        <v>253</v>
-      </c>
-      <c r="H45" s="3">
-        <v>708</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D46" s="3">
-        <v>1.9403E-2</v>
-      </c>
-      <c r="E46" s="3">
-        <v>115</v>
-      </c>
-      <c r="F46" s="3">
-        <v>235</v>
-      </c>
-      <c r="H46" s="3">
-        <v>708</v>
-      </c>
-      <c r="I46" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D47" s="3">
-        <v>1.7330000000000002E-2</v>
-      </c>
-      <c r="E47" s="3">
-        <v>120</v>
-      </c>
-      <c r="F47" s="3">
-        <v>144</v>
-      </c>
-      <c r="H47" s="3">
-        <v>708</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A48" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D48" s="3">
-        <v>2.1069999999999998E-2</v>
-      </c>
-      <c r="E48" s="3">
-        <v>120</v>
-      </c>
-      <c r="F48" s="3">
-        <v>144</v>
-      </c>
-      <c r="H48" s="3">
-        <v>708</v>
-      </c>
-      <c r="I48" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D49" s="3">
-        <v>5.3449999999999999E-3</v>
-      </c>
-      <c r="E49" s="3">
-        <v>120</v>
-      </c>
-      <c r="F49" s="3">
-        <v>144</v>
-      </c>
-      <c r="H49" s="3">
-        <v>708</v>
-      </c>
-      <c r="I49" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D50" s="3">
-        <v>1.7330000000000002E-2</v>
-      </c>
-      <c r="E50" s="3">
-        <v>120</v>
-      </c>
-      <c r="F50" s="3">
-        <v>225</v>
-      </c>
-      <c r="H50" s="3">
-        <v>708</v>
-      </c>
-      <c r="I50" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K50" s="3">
-        <v>1</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D51" s="3">
-        <v>2.8885000000000001E-2</v>
-      </c>
-      <c r="E51" s="3">
-        <v>120</v>
-      </c>
-      <c r="F51" s="3">
-        <v>140</v>
-      </c>
-      <c r="H51" s="3">
-        <v>708</v>
-      </c>
-      <c r="I51" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K51" s="3">
-        <v>1</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D52" s="3">
-        <v>1.5386E-2</v>
-      </c>
-      <c r="E52" s="3">
-        <v>120</v>
-      </c>
-      <c r="F52" s="3">
-        <v>144</v>
-      </c>
-      <c r="H52" s="3">
-        <v>708</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D53" s="3">
-        <v>3.9204000000000003E-2</v>
-      </c>
-      <c r="E53" s="3">
-        <v>120</v>
-      </c>
-      <c r="H53" s="3">
-        <v>708</v>
-      </c>
-      <c r="I53" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K53" s="3">
-        <v>1</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="D54" s="3">
-        <v>5.1914000000000002E-2</v>
-      </c>
-      <c r="E54" s="3">
-        <v>85</v>
-      </c>
-      <c r="F54" s="3">
-        <v>297</v>
-      </c>
-      <c r="H54" s="3">
-        <v>708</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="D55" s="3">
-        <v>3.3673279061519699E-2</v>
-      </c>
-      <c r="E55" s="3">
-        <v>120</v>
-      </c>
-      <c r="F55" s="3">
-        <v>225</v>
-      </c>
-      <c r="H55" s="3">
-        <v>708</v>
-      </c>
-      <c r="I55" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K55" s="3">
-        <v>1</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D56" s="3">
-        <v>4.25034931994452E-2</v>
-      </c>
-      <c r="E56" s="3">
-        <v>120</v>
-      </c>
-      <c r="F56" s="3">
-        <v>225</v>
-      </c>
-      <c r="H56" s="3">
-        <v>708</v>
-      </c>
-      <c r="I56" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K56" s="3">
-        <v>1</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D57" s="3">
-        <v>3.3515999999999997E-2</v>
-      </c>
-      <c r="E57" s="3">
-        <v>120</v>
-      </c>
-      <c r="F57" s="3">
-        <v>225</v>
-      </c>
-      <c r="H57" s="3">
-        <v>708</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A58" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D58" s="3">
-        <v>2.9884999999999998E-2</v>
-      </c>
-      <c r="E58" s="3">
-        <v>120</v>
-      </c>
-      <c r="F58" s="3">
-        <v>225</v>
-      </c>
-      <c r="H58" s="3">
-        <v>708</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A59" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D59" s="3">
-        <v>2.6974999999999999E-2</v>
-      </c>
-      <c r="E59" s="3">
-        <v>120</v>
-      </c>
-      <c r="F59" s="3">
-        <v>161</v>
-      </c>
-      <c r="H59" s="3">
-        <v>708</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D60" s="3">
-        <v>4.9220000000000002E-3</v>
-      </c>
-      <c r="E60" s="3">
-        <v>120</v>
-      </c>
-      <c r="F60" s="3">
-        <v>144</v>
-      </c>
-      <c r="H60" s="3">
-        <v>708</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A61" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D61" s="3">
-        <v>4.4047999999999997E-2</v>
-      </c>
-      <c r="E61" s="3">
-        <v>120</v>
-      </c>
-      <c r="F61" s="3">
-        <v>225</v>
-      </c>
-      <c r="H61" s="3">
-        <v>708</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A62" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="D62" s="3">
-        <v>2.5055999999999998E-2</v>
-      </c>
-      <c r="E62" s="3">
-        <v>95</v>
-      </c>
-      <c r="F62" s="3">
-        <v>253</v>
-      </c>
-      <c r="H62" s="3">
-        <v>708</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A63" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D63" s="3">
-        <v>5.1914000000000002E-2</v>
-      </c>
-      <c r="E63" s="3">
-        <v>85</v>
-      </c>
-      <c r="F63" s="3">
-        <v>297</v>
-      </c>
-      <c r="H63" s="3">
-        <v>708</v>
-      </c>
-      <c r="I63" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K63" s="3">
-        <v>1</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A64" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D64" s="3">
-        <v>4.25034931994452E-2</v>
-      </c>
-      <c r="E64" s="3">
-        <v>120</v>
-      </c>
-      <c r="F64" s="3">
-        <v>225</v>
-      </c>
-      <c r="H64" s="3">
-        <v>708</v>
-      </c>
-      <c r="I64" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K64" s="3">
-        <v>1</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A65" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D65" s="3">
-        <v>2.8528000000000001E-2</v>
-      </c>
-      <c r="E65" s="3">
-        <v>120</v>
-      </c>
-      <c r="F65" s="3">
-        <v>225</v>
-      </c>
-      <c r="H65" s="3">
-        <v>708</v>
-      </c>
-      <c r="I65" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K65" s="3">
-        <v>1</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A66" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D66" s="3">
-        <v>2.8528000000000001E-2</v>
-      </c>
-      <c r="E66" s="3">
-        <v>120</v>
-      </c>
-      <c r="F66" s="3">
-        <v>225</v>
-      </c>
-      <c r="H66" s="3">
-        <v>708</v>
-      </c>
-      <c r="I66" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A67" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D67" s="3">
-        <v>2.2934E-2</v>
-      </c>
-      <c r="E67" s="3">
-        <v>120</v>
-      </c>
-      <c r="F67" s="3">
-        <v>140</v>
-      </c>
-      <c r="H67" s="3">
-        <v>708</v>
-      </c>
-      <c r="I67" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K67" s="3">
-        <v>1</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A68" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D68" s="3">
-        <v>3.9204000000000003E-2</v>
-      </c>
-      <c r="E68" s="3">
-        <v>120</v>
-      </c>
-      <c r="F68" s="3">
-        <v>225</v>
-      </c>
-      <c r="H68" s="3">
-        <v>708</v>
-      </c>
-      <c r="I68" s="3">
-        <v>2750</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K68" s="3">
-        <v>1</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A69" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D69" s="16">
-        <v>4.7503619965347202E-2</v>
-      </c>
-      <c r="E69" s="1">
-        <v>90</v>
-      </c>
-      <c r="F69" s="1">
-        <v>416</v>
-      </c>
-      <c r="G69" s="1">
-        <v>37.44</v>
-      </c>
-      <c r="H69" s="1">
-        <v>354</v>
-      </c>
-      <c r="I69" s="1">
-        <v>1001</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M69" s="17" t="s">
-        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -6490,912 +6576,911 @@
   <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.08984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
         <v>204</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="D4" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>207</v>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="D12" t="s">
         <v>217</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="B14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18" t="s">
         <v>225</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" t="s">
         <v>228</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="D20" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+      <c r="B22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
+      <c r="B23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="B24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
+      <c r="B25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+      <c r="B26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
+      <c r="B27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
+      <c r="B28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+      <c r="B29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>204</v>
+      </c>
+      <c r="D29" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
+      <c r="B30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
+      <c r="B31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
+      <c r="B32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
+      <c r="B33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>228</v>
+      </c>
+      <c r="D33" t="s">
         <v>242</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="B34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
+      <c r="C35" t="s">
+        <v>228</v>
+      </c>
+      <c r="D35" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" t="s">
+        <v>228</v>
+      </c>
+      <c r="D36" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
+      <c r="B37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="B38" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" t="s">
+        <v>204</v>
+      </c>
+      <c r="D38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
+      <c r="B39" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
+      <c r="B40" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" t="s">
+        <v>204</v>
+      </c>
+      <c r="D40" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
+      <c r="B41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" t="s">
+        <v>204</v>
+      </c>
+      <c r="D41" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
+      <c r="B42" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
+      <c r="B43" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" t="s">
+        <v>204</v>
+      </c>
+      <c r="D43" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
+      <c r="B44" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" t="s">
+        <v>204</v>
+      </c>
+      <c r="D44" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
+      <c r="B45" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" t="s">
+        <v>204</v>
+      </c>
+      <c r="D45" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
+      <c r="B46" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C46" t="s">
+        <v>204</v>
+      </c>
+      <c r="D46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
+      <c r="B47" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" t="s">
+        <v>204</v>
+      </c>
+      <c r="D47" t="s">
         <v>258</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D47" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="4" t="s">
+      <c r="C48" t="s">
+        <v>204</v>
+      </c>
+      <c r="D48" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B49" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" t="s">
+        <v>204</v>
+      </c>
+      <c r="D49" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
+      <c r="B50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="4" t="s">
+      <c r="B51" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="4" t="s">
+      <c r="B52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
+      <c r="B53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
+      <c r="B54" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" t="s">
+        <v>216</v>
+      </c>
+      <c r="D54" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="4" t="s">
+      <c r="B55" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" t="s">
+        <v>216</v>
+      </c>
+      <c r="D55" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
+      <c r="B56" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" t="s">
+        <v>204</v>
+      </c>
+      <c r="D56" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="4" t="s">
+      <c r="B57" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="4" t="s">
+      <c r="C58" t="s">
+        <v>204</v>
+      </c>
+      <c r="D58" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B59" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" t="s">
+        <v>204</v>
+      </c>
+      <c r="D59" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="4" t="s">
+      <c r="B60" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" t="s">
+        <v>216</v>
+      </c>
+      <c r="D60" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="4" t="s">
+      <c r="B61" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" t="s">
+        <v>228</v>
+      </c>
+      <c r="D61" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="4" t="s">
+      <c r="B62" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" t="s">
+        <v>228</v>
+      </c>
+      <c r="D62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="4" t="s">
+      <c r="B63" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C63" t="s">
+        <v>228</v>
+      </c>
+      <c r="D63" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="4" t="s">
+      <c r="B64" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" t="s">
+        <v>204</v>
+      </c>
+      <c r="D64" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="4" t="s">
+      <c r="B65" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C65" t="s">
+        <v>204</v>
+      </c>
+      <c r="D65" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>117</v>
+      <c r="B66" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -7408,735 +7493,734 @@
   <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="78.36328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="78.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B23" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B24" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B26" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B29" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B30" t="s">
+        <v>222</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B32" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B35" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B36" t="s">
+        <v>210</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B37" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C10" s="5" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B38" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B39" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B40" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B41" t="s">
+        <v>207</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B42" t="s">
+        <v>210</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C34" s="5" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B44" t="s">
+        <v>210</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B45" t="s">
+        <v>222</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B46" t="s">
+        <v>222</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B47" t="s">
+        <v>207</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C38" s="5" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A51" s="5" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" s="5" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A53" s="5" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" s="5" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" s="5" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" s="5" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" s="5" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" s="5" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" s="5" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" s="5" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" s="5" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" s="5" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A63" s="5" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A64" s="5" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="5" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" s="5" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" s="5" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" s="5" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" s="5" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" s="5" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" s="5" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" s="4" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A73" s="5" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A75" s="5" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A76" s="5" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A77" s="5" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" s="4" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A79" s="5" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A80" s="5" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" s="5" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A82" s="5" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A83" s="5" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" s="5" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A85" s="5" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A86" s="5" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A87" s="5" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A88" s="5" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A89" s="5" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" s="8" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A90" s="5" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A91" s="9" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -8146,6 +8230,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F97ADFFCC3946448ACC17B0A5ACE749" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="be0a48681047e911b15f2a2e43b2478c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8ac244d9-c0f9-4830-920a-ea29ecd4a534" xmlns:ns4="17755de4-8554-4f42-8551-46a8bd5823bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bad0b40a94fb30399178fa1e2724f374" ns3:_="" ns4:_="">
     <xsd:import namespace="8ac244d9-c0f9-4830-920a-ea29ecd4a534"/>
@@ -8384,7 +8477,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="8ac244d9-c0f9-4830-920a-ea29ecd4a534" xsi:nil="true"/>
@@ -8392,16 +8485,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB642855-A075-4C9B-A97B-CD933E5E5721}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75A5E3AE-C450-451E-ADC4-F528AB51A6A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8420,7 +8512,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CDECD2F-094C-4BA0-BD61-057A1DCCF8DE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="17755de4-8554-4f42-8551-46a8bd5823bb"/>
@@ -8435,12 +8527,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB642855-A075-4C9B-A97B-CD933E5E5721}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>